--- a/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>441_蓝星球_Echinops_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010101030303015300</v>
+        <v>030101010303030153010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>333_狼尾草_wolf tail grass_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>334_狗尾草_puppy tail grass_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>816_山里红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>431_小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>3</v>
+      </c>
+      <c r="C19" t="str">
+        <v>574_迷你菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F20" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030101010303030153010</v>
+        <v>0301010103030301530104030101010101015120</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301010103030301530104030101010101015120</v>
+        <v>03010101030303015301040301010101010151210</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F22" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>4</v>
+      </c>
+      <c r="C26" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>832_康乃馨香槟_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +744,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03010101030303015301040301010101010151210</v>
+        <v>030101010303030153010403010101010101512101551515141010550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
@@ -686,6 +686,9 @@
       <c r="C31" t="str">
         <v>832_康乃馨香槟_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -744,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030101010303030153010403010101010101512101551515141010550</v>
+        <v>030101010303030153010403010101010101512101551515141010555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -684,15 +684,98 @@
     </row>
     <row r="31">
       <c r="C31" t="str">
-        <v>832_康乃馨香槟_undefined_undefined_1bunch</v>
+        <v>616_康乃馨紫精灵_Purple Elves_undefined_20stems</v>
       </c>
       <c r="F31" t="str">
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>5</v>
+      </c>
+      <c r="C32" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>832_康乃馨香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>6</v>
+      </c>
+      <c r="C39" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -747,7 +830,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030101010303030153010403010101010101512101551515141010555</v>
+        <v>030101010303030153010403010101010101512101551515141010555651410155525200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
@@ -772,6 +772,9 @@
       <c r="C41" t="str">
         <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -830,7 +833,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030101010303030153010403010101010101512101551515141010555651410155525200</v>
+        <v>030101010303030153010403010101010101512101551515141010555651410155525205</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-9-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -776,9 +776,79 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>7</v>
+      </c>
+      <c r="C44" t="str">
+        <v>601_康乃馨大红_red_undefined_20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>568_玫瑰果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F48" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>8</v>
+      </c>
+      <c r="C49" t="str">
+        <v>452_粉吊鸟_pink hanging heliconia_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L49"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -833,7 +903,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030101010303030153010403010101010101512101551515141010555651410155525205</v>
+        <v>0301010103030301530104030101010101015121015515151410105556514101555252051010515105530</v>
       </c>
     </row>
   </sheetData>
